--- a/www/download/COUNTRY.LTU.rpA2.xlsx
+++ b/www/download/COUNTRY.LTU.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Lituânia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3.99999999710861</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4.00000001825342</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999998659746</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.9999999995881</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999559562</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999588469</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999905712</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3.6655545966935</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3.05558102643111</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.77785491279575</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.76969939037289</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2.74982120464169</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2.52016123792344</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2.34585943266422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2.47782342361756</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>4.85565515775713</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>4.57846548825072</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>4.53674182390031</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>3.54296670880097</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>3.28190962727195</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>3.51516555783293</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.346</t>
+          <t>3.68725297164638</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>3.42432962459274</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>3.32217555662053</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>3.74076985231603</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>3.68534538817369</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>3.56375886432681</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>3.88817002367281</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>3.59376542409794</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>3.59460289863311</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>3.04943422863649</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>2.85749448636563</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>2.83164275709472</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>2.37324093346177</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>2.20192593212041</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>2.27477707313362</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>2.30295901059937</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>2.18448730149816</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1.86472795000284</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>2.2744371807945</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>2.19412277232584</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>2.10313111621365</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>2.15081884805971</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>2.02009882556189</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>2.09799200491953</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2571.545</t>
+          <t>0.996673350925474</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2595.514</t>
+          <t>0.857597995012979</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2602.912</t>
+          <t>0.818663895479369</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2659.424</t>
+          <t>0.655060548149483</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2522.551</t>
+          <t>0.606060172965545</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2583.224</t>
+          <t>0.643581699420447</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2464.605</t>
+          <t>0.614500197392354</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2513.641</t>
+          <t>0.568121322804065</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2546.154</t>
+          <t>0.169011695739464</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2578.763</t>
+          <t>0.587678373287051</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2732.644</t>
+          <t>0.541016893949665</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2760.572</t>
+          <t>0.485239131168475</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2868.389</t>
+          <t>0.249112249961824</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2915.074</t>
+          <t>0.109858398977363</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2692.609</t>
+          <t>0.100148845567563</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2087.973</t>
+          <t>9196313298.72705</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1988.28</t>
+          <t>8943948544.96193</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1990.438</t>
+          <t>8189354061.08444</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076.019</t>
+          <t>8544413843.22647</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2016.758</t>
+          <t>8064324575.74819</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2079.554</t>
+          <t>8298306593.52463</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1980.536</t>
+          <t>8111553986.41082</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2019.223</t>
+          <t>8204021989.45934</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2053.925</t>
+          <t>8500947288.46793</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2112.124</t>
+          <t>8329310317.05566</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2274.689</t>
+          <t>8886065633.26609</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2341.042</t>
+          <t>8827920477.60279</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2475.446</t>
+          <t>9234985356.04117</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2553.702</t>
+          <t>9859705307.29493</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2306.659</t>
+          <t>8696933409.22788</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>1545578460.19967</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>1554287662.54128</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>1560480120.26359</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>1875108353.62609</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>1921060746.49793</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>1924435678.24025</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>1806054255.93329</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>1927487226.77709</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>2142277175.18556</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>1962570071.40436</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>2171253940.47866</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>2298343217.93941</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>2377828928.38884</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>2610198418.68133</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>2360137729.14182</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>23262654.1341633</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>18640878.7902145</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>56.27</t>
+          <t>15478161.8547628</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.54</t>
+          <t>14111900.5586227</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>14382374.8823997</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>14024042.566014</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>12801616.9200306</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>11348273.805344</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>9280429.60793768</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>7332763.20824603</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>6742703.7381126</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>5908017.39377529</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>4941485.37361125</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>4226833.49673512</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>4971088.49478632</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>24058.4199887696</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>23932.5420318964</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>22788.6549673777</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>23059.7296315208</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>22250.3818598445</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>23354.4042381825</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>21558.3349719059</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>21723.5731306023</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>23966.1397770761</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>26200.7466272596</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>29920.6018379749</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>30738.2821259568</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>36597.4180111103</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>40419.2857587968</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>34439.6941941949</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>40115.6918790942</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>38895.6955080076</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>35026.9863715458</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>36095.1781562173</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>35148.3586475934</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>36374.4770732898</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>34299.1887312282</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>35136.1494839467</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>38980.3641949664</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>41424.6006992877</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47007.0857898274</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>48604.196370112</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>56999.5278244802</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>66478.4202078018</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>54199.730352849</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>3.69736620911936</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>3.48808883227878</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>3.43083816326461</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>2.75256343917978</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2.56126584726751</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>2.70650083950323</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>2.79229419644174</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>2.62889311821161</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>2.36056275170388</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.89</t>
+          <t>2.8485111680157</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>2.80247155474506</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>2.69706412096064</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>2.83345542270438</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>2.66840268048593</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>2.76483594673552</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1392.3987857604</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1577.94541662314</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1859.27887218759</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1957.24631743657</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1970.09256789277</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2092.75656972439</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2353.13364660797</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2649.18477311275</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>3237.88281306627</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3838.67502997525</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4438.3889803169</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>5125.08748123012</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>6478.83406944057</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>7785.76745287189</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>7146.10989932949</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.99999999710861</t>
+          <t>1285.19745567908</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.00000001825342</t>
+          <t>1352.37767557755</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.99999998659746</t>
+          <t>1359.06646948579</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.9999999995881</t>
+          <t>1580.36945101229</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.99999999559562</t>
+          <t>1649.12073697135</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.99999999588469</t>
+          <t>1712.43609026539</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.99999999905712</t>
+          <t>1674.59829015604</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.6655545966935</t>
+          <t>1731.95006449554</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05558102643111</t>
+          <t>1890.63381447847</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.77785491279575</t>
+          <t>1693.62277477077</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.76969939037289</t>
+          <t>1793.38724744252</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.74982120464169</t>
+          <t>1835.59078183804</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.52016123792344</t>
+          <t>1802.61460722374</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.34585943266422</t>
+          <t>1942.40096642457</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.47782342361756</t>
+          <t>1897.98372133348</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-680116534.167692</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-639623757.463619</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-594955395.262889</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-506150111.55161</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-219280106.696824</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-109608188.155166</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-23219135.0352555</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>244985.450411197</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>180918791.332463</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>14996914.4017196</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-55235935.5364375</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-95388906.0710015</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-190315408.221948</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>116134613.18353</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>199883946.476179</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-776044595.741894</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-749258381.025113</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-721930278.671935</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-620258197.160436</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-317075386.884659</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-239077958.567438</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-196512676.588657</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-229729997.884978</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-93180912.3935871</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-249782139.637935</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-402608750.09541</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-482955984.830183</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-699081819.70874</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-329652870.462727</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-310211732.273348</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>95928061.5742018</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>109634623.561495</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>126974883.409047</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>114108085.608826</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>97795280.1878347</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>129469770.412272</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>173293541.553401</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>229974983.335389</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>274099703.72605</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>264779054.039654</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>347372814.558973</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>387567078.759182</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>508766411.486792</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>445787483.646257</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>510095678.749527</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6037.04310035311</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6069.59114278272</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>6021.80357941095</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5930.43662226536</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5872.9573585967</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>6347.14580616431</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>6350.56937713002</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6285.06167013403</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>6353.59357404819</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6517.92616311103</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>6819.30399504274</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>6786.2968202995</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>6910.24274110798</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>7125.50891181034</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7145.59734039515</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5874.27266998547</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>5853.30243230217</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5791.29281961681</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>5772.56913412366</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>5576.53538189937</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>6020.32646040495</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>6031.56999877041</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5973.30940560798</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>5973.21932842921</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6191.16559844148</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6552.27833429067</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6552.15625040956</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>6752.49213425511</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>7037.10249922605</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>7022.92173812685</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>485.57</t>
+          <t>2785.35475277992</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>457.85</t>
+          <t>3540.9300159829</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>453.67</t>
+          <t>4435.34973971317</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>354.3</t>
+          <t>4160.90500981388</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>328.19</t>
+          <t>3524.99083892768</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>351.52</t>
+          <t>4403.01337789616</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>368.73</t>
+          <t>5178.13508376535</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>342.43</t>
+          <t>5887.63000237662</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>332.22</t>
+          <t>7706.11485602183</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>374.08</t>
+          <t>9118.8685379579</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>368.53</t>
+          <t>12140.3079666271</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>356.38</t>
+          <t>14416.2990549895</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>388.82</t>
+          <t>17142.913254606</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>359.38</t>
+          <t>23876.027783493</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>359.46</t>
+          <t>17610.1738120431</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>304.94</t>
+          <t>1973229757.0705</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>285.75</t>
+          <t>1906378114.10012</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>283.16</t>
+          <t>1959371086.77489</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>237.32</t>
+          <t>1846383547.89633</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>220.19</t>
+          <t>1656787280.09481</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>227.48</t>
+          <t>1894399817.29494</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>230.3</t>
+          <t>1991369423.35781</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>218.45</t>
+          <t>2034275115.56347</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>186.47</t>
+          <t>2187115819.12887</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>227.44</t>
+          <t>1889822738.09679</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>219.41</t>
+          <t>2261052081.30944</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>210.31</t>
+          <t>2328463719.11456</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>215.08</t>
+          <t>2341329904.73889</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>202.01</t>
+          <t>2656963520.16961</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>209.8</t>
+          <t>2429153225.90265</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>99.67</t>
+          <t>3526.51382046901</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>4409.395665596</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>5563.63210469451</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.51</t>
+          <t>5658.86379586788</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>4855.91104604275</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>5338.12529778591</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>6119.8313817904</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>7063.11434683333</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>9191.95625324947</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>58.77</t>
+          <t>11091.372515054</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>14441.4051098642</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>17761.9081874317</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>22277.3042327746</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>29376.4381969645</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>18317.813610085</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8695.098</t>
+          <t>1506253849.38149</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8741.907</t>
+          <t>1511192142.55612</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8701.417</t>
+          <t>1659783654.69121</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8603.437</t>
+          <t>1757570673.50415</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8126.127</t>
+          <t>1822582439.79359</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8423.641</t>
+          <t>2061234215.40297</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8117.89</t>
+          <t>2263081289.87685</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8332.169</t>
+          <t>2402024857.40475</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8517.213</t>
+          <t>2807981158.06766</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8825.507</t>
+          <t>2446325019.94938</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9570.913</t>
+          <t>2794165421.49705</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9746.988</t>
+          <t>3019231264.78331</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10323.885</t>
+          <t>3222135304.81304</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10771.992</t>
+          <t>3810934433.95202</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10133.247</t>
+          <t>2777932935.27064</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7260.148</t>
+          <t>-741.15906768909</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6975.781</t>
+          <t>-868.465649613101</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6914.235</t>
+          <t>-1128.28236498135</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7036.463</t>
+          <t>-1497.958786054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6841.408</t>
+          <t>-1330.92020711507</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7132.922</t>
+          <t>-935.11191988976</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6849.089</t>
+          <t>-941.696298025052</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6994.645</t>
+          <t>-1175.48434445671</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7199.257</t>
+          <t>-1485.84139722765</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7552.973</t>
+          <t>-1972.50397709605</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8256.131</t>
+          <t>-2301.09714323712</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8497.122</t>
+          <t>-3345.60913244218</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>9115.301</t>
+          <t>-5134.39097816862</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>9575.259</t>
+          <t>-5500.41041347152</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8885.531</t>
+          <t>-707.639798041871</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9196.313</t>
+          <t>466975907.689003</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8943.949</t>
+          <t>395185971.544001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8189.354</t>
+          <t>299587432.083674</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8544.414</t>
+          <t>88812874.3921803</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8064.325</t>
+          <t>-165795159.698774</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8298.307</t>
+          <t>-166834398.108027</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8111.554</t>
+          <t>-271711866.519045</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8204.022</t>
+          <t>-367749741.841282</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8500.947</t>
+          <t>-620865338.938791</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8329.31</t>
+          <t>-556502281.852594</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8886.066</t>
+          <t>-533113340.187605</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8827.92</t>
+          <t>-690767545.668752</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9234.985</t>
+          <t>-880805400.074147</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9859.705</t>
+          <t>-1153970913.7824</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8696.933</t>
+          <t>-348779709.367993</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3247.55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>4107.62498</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>4884.125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>5344.84999</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>5082.15008</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>5179.55</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>5518.45004</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>6309.08615</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8480.41658</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>10617.22104</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>12152.58224</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>13964.39876</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>17812.98732</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>21228.38204</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>15968.43085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5515.267</t>
+          <t>0.0687741897736268</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5503.216</t>
+          <t>0.0576937410506823</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5328.017</t>
+          <t>0.0721409061041283</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5458.676</t>
+          <t>0.0752591958343908</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5105.055</t>
+          <t>0.071798425050771</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5327.967</t>
+          <t>0.0886671422505292</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5098.418</t>
+          <t>0.0896006143369258</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5072.288</t>
+          <t>0.096398292779201</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5226.603</t>
+          <t>0.1068456720524</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5268.226</t>
+          <t>0.108786705094041</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5656.093</t>
+          <t>0.110923465021113</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5582.956</t>
+          <t>0.104226380077007</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5929.463</t>
+          <t>0.101543666623191</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5994.761</t>
+          <t>0.0939490246155326</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5526.222</t>
+          <t>0.0714930308406639</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2504.97500744375</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>3185.72497070167</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>3915.82503481901</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>4674.57499957807</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>4707.72500997286</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>4508.299991816</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>4631.35001721752</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>5473.03260370754</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>7280.6121051987</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>9086.21960703123</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>10621.4053437327</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>12904.6207284722</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>16887.3322519144</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>21323.5323202352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>16682.5566681587</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1545.578</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1554.288</t>
+          <t>4413.2116762702</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1560.48</t>
+          <t>4810.78304557858</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1875.108</t>
+          <t>5513.89748690017</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1921.061</t>
+          <t>5373.96564117383</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1924.436</t>
+          <t>5163.52928834904</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1806.054</t>
+          <t>5423.21665241783</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1927.487</t>
+          <t>6355.59458427306</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2142.277</t>
+          <t>8402.73777334017</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1962.57</t>
+          <t>10486.1630721106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2171.254</t>
+          <t>12126.7510595509</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2298.343</t>
+          <t>14490.2804927815</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2377.829</t>
+          <t>19059.9184852712</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2610.198</t>
+          <t>23934.7048099527</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2360.138</t>
+          <t>18804.4211754875</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>369.74</t>
+          <t>24600.7898997101</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>348.81</t>
+          <t>27546.6244373116</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>343.08</t>
+          <t>30603.485199467</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>275.26</t>
+          <t>31813.1379045267</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>256.13</t>
+          <t>32026.7029437954</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>270.65</t>
+          <t>32640.4917139336</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>279.23</t>
+          <t>33887.0412155523</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>262.89</t>
+          <t>37548.8012106701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>236.06</t>
+          <t>47207.3276034981</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>284.85</t>
+          <t>55893.2189614342</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>62765.6060762895</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>269.71</t>
+          <t>72359.252719093</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>283.35</t>
+          <t>93978.2073332064</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>266.84</t>
+          <t>115669.457151328</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>276.48</t>
+          <t>102329.524978285</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>23.263</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18.641</t>
+          <t>3647.69272428469</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.478</t>
+          <t>3627.32457554207</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14.112</t>
+          <t>3993.82412836323</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14.382</t>
+          <t>3970.65942851008</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.024</t>
+          <t>3851.35197013299</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.802</t>
+          <t>4095.94484300415</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.348</t>
+          <t>4385.76814554866</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>4887.15773120033</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>5340.7093261259</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>5713.95903946836</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5.908</t>
+          <t>6311.66165310784</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.941</t>
+          <t>7067.72863079353</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>7387.65518169046</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.971</t>
+          <t>6483.95376910765</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2504.97500744375</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2657.11121643758</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2939.42878253037</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3329.00648439264</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3412.31095538772</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3237.98370956394</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3330.82440010191</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3612.69539104058</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>4043.94705554353</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4417.79952482758</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>4874.89543464886</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5542.76286926896</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6135.93360606634</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6441.95147274622</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>5475.74598192922</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3084.29817890418</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3167.2132337298</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4067.04202442142</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4351.47749309983</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4269.55939882617</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4986.89569165096</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5389.43335758217</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6268.82510572694</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8281.78145665983</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>9919.11415788945</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11400.5674904491</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12666.8304572185</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16021.7258247288</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>18652.8001300473</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14461.9577845125</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7260148032.48465</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6975781100.40018</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6914234869.87965</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7036463052.31785</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6841408027.0293</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7132922456.96746</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6849089073.23472</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6994645132.69216</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7199256878.75401</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>7552972837.81307</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>8256131346.79825</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8497122248.69701</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>9115301199.79553</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>9575258875.69074</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>8885531361.91987</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8695098406.1125</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8741907182.64329</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8701417461.47426</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8603437037.49791</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8126127358.50377</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8423640783.39861</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8117890061.3451</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8332169289.88257</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8517213440.40721</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8825506560.57832</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9570912962.89838</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9746987638.10926</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10323885224.0626</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10771991781.5595</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10133246949.737</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5515267400.99386</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5503216273.3625</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5328016579.10688</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5458675733.13771</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5105054920.23628</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5327966812.74797</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5098417905.80103</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5072288064.30586</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5226603064.40357</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5268225776.78454</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5656092634.79602</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5582956421.28812</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5929463493.84259</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5994761082.88008</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5526221719.02264</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1480200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1493500</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1502500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1490400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1457200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1399200</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1345900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1394900</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1425900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1425500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1460700</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1487600</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1528900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1530742.48708814</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1442881.941105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1202600</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1149300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1148200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1186500</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1164900</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1123800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1078500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1112900</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1133100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1158800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1210700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1252100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1319100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1343800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1243497.35069574</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2571545000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2595513640.41746</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2602912000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2659424000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2522551000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2583224000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2464604694.9485</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2513640732.24568</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2546154000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2578763000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2732644442.90056</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2760571519.06275</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2868389000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2915073729.0729</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2692608724.27263</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2087973000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1988280000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1990438000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2076018674.27178</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2016758000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2079554000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1980536270.47619</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2019223254.9505</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2053925000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2112123969.96663</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2274689000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2341041784.49537</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2475446000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2553701952.54095</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2306658737.99467</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.38297454039357</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.374950919159893</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.365446441330267</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.354082269774032</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.344615980455163</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.346596133326365</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.34174830988491</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.345725669120357</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.342606166961938</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.366551899886692</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.379590543195016</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.382423371633458</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.383804148482609</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.391863244594682</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.401402104157042</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.551165908038753</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.56012188209631</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.562656144083645</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.565446055716564</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.58347578064208</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.584354733603416</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.589745862974171</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.587979910136802</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.579241250905231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.571140274425083</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.562470444100666</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.562069271680628</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.545168024157812</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.543979820692733</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.532984201290888</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0658595515676768</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0649271987437972</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0718974145860885</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0804716745094041</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0719082389027571</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0690491330702188</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0685058271409187</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0662944207428411</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0781525821328311</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0623078256882247</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0579390127043173</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0555073566859132</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0710278273595789</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0641569347125852</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0656136945520701</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.465057971336289</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.458407948288268</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.450844210371361</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.442417743916483</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.428675170993141</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.432678626367677</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.435437582968223</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.443663284304168</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.465270116015049</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.464322489564079</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.478724732434004</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.482193462315508</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.502041307075269</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.511366793939143</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.526037135464151</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.506549288430407</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.513667978527083</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.518182771576184</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.522967324742578</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.540044830272503</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.53712858467267</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.534966344389864</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.528275162064775</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.508974644900184</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.508910915288742</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.496966817573052</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.494652298290051</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.473078588627013</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.469788667811106</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.456498821086226</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0283927402333042</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0279240731846492</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0309730180524542</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0346149313409398</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0312799987343556</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0301927889596535</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0295960726419121</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0280615536310571</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0257552390847668</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0267665951471784</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0243084499929435</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0231542393944408</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0248801042977179</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0188445382497515</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0174640434496225</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13012.95002</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>16011.72486</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17948.70002</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>19579.40021</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>18273.80013</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>19248.7999</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20729.19991</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24205.77749</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>31550.79177</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>38827.22596</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>45762.79956</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>53512.71586</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>68779.84557</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>87380.2149</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>63756.94838</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6015.75001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7580.42491</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8877.82507</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9865.37498</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9643.52504</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10150.42498</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10812.65001</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>12624.41969</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>16684.51923</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20405.27723</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23527.31855</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>27157.11095</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>35081.64431</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>42587.50494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>33266.37896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>98403.1598270781</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>101377.408978468</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>105819.601650491</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>111683.194777985</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>116521.856497935</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>120126.189828282</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>124588.862428806</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>129644.249343817</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>135812.082947234</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>143521.622402548</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>152146.281960362</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>163093.292643572</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>177643.798404054</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>190049.299326338</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>192823.545110645</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
